--- a/Methanol/Methanol_Sensitivität/Sensitivitäten.xlsx
+++ b/Methanol/Methanol_Sensitivität/Sensitivitäten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_Sensitivität\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B069B10-672E-4DBD-AE63-795DE59EEEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CADCC24-D5CC-46C2-95B9-6C348E9782FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-6885" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6945" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="171">
   <si>
     <t>Wert</t>
   </si>
@@ -495,40 +495,61 @@
     <t>h2_preis</t>
   </si>
   <si>
-    <t>annuity_dac</t>
-  </si>
-  <si>
-    <t>result_dac_leistung</t>
-  </si>
-  <si>
-    <t>result_dac_flowsum_elin</t>
-  </si>
-  <si>
-    <t>result_dac_flowsum_qin</t>
-  </si>
-  <si>
-    <t>result_dac_flowsum_co2out</t>
-  </si>
-  <si>
-    <t>calc_gesamtinvest_dac</t>
-  </si>
-  <si>
-    <t>calc_opex_fix_dac</t>
-  </si>
-  <si>
-    <t>calc_annuity_dac</t>
-  </si>
-  <si>
-    <t>calc_verzinstinvest_dac</t>
-  </si>
-  <si>
-    <t>calc_cost_dac</t>
-  </si>
-  <si>
-    <t>calc_lcon_dac</t>
-  </si>
-  <si>
-    <t>€/ kg a</t>
+    <t>annuity_mea</t>
+  </si>
+  <si>
+    <t>result_mea_leistung</t>
+  </si>
+  <si>
+    <t>result_mea_flowsum_elin</t>
+  </si>
+  <si>
+    <t>result_mea_flowsum_qin</t>
+  </si>
+  <si>
+    <t>result_mea_flowsum_biogasin</t>
+  </si>
+  <si>
+    <t>kg_Biogas/a</t>
+  </si>
+  <si>
+    <t>result_mea_flowsum_co2out</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_mea</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_mea</t>
+  </si>
+  <si>
+    <t>calc_opex_var_mea</t>
+  </si>
+  <si>
+    <t>calc_annuity_mea</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_mea</t>
+  </si>
+  <si>
+    <t>calc_cost_mea</t>
+  </si>
+  <si>
+    <t>€ / kg a</t>
+  </si>
+  <si>
+    <t>result_biogasbezug_flowsum</t>
+  </si>
+  <si>
+    <t>kg_CH4/a</t>
+  </si>
+  <si>
+    <t>calc_biogasbezug_kosten</t>
+  </si>
+  <si>
+    <t>result_h2bezug_flowsum</t>
+  </si>
+  <si>
+    <t>calc_h2bezug_kosten</t>
   </si>
 </sst>
 </file>
@@ -538,7 +559,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,12 +575,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -569,7 +584,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -595,20 +610,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -621,8 +627,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -909,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -968,18 +972,34 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1699</v>
+      </c>
+      <c r="C4">
+        <f>B4*0.7</f>
+        <v>0.11892999999999999</v>
+      </c>
+      <c r="D4">
+        <f>B4*1.3</f>
+        <v>0.22087000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="2">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="C4" s="2">
-        <f>B4-0.02</f>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="D4" s="2">
-        <f>B4+0.02</f>
-        <v>4.8000000000000001E-2</v>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <f>B5-0.02</f>
+        <v>-0.02</v>
+      </c>
+      <c r="D5" s="2">
+        <f>B5+0.02</f>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -1031,13 +1051,13 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1053,7 +1073,7 @@
       <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
@@ -1064,7 +1084,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
+      <c r="A10" s="9"/>
       <c r="B10" t="s">
         <v>24</v>
       </c>
@@ -1073,7 +1093,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
+      <c r="A11" s="9"/>
       <c r="B11" t="s">
         <v>25</v>
       </c>
@@ -1082,7 +1102,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
+      <c r="A12" s="9"/>
       <c r="B12" t="s">
         <v>26</v>
       </c>
@@ -1091,7 +1111,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
+      <c r="A13" s="9"/>
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1100,7 +1120,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
+      <c r="A14" s="9"/>
       <c r="B14" t="s">
         <v>28</v>
       </c>
@@ -1109,7 +1129,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
+      <c r="A15" s="9"/>
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -1118,7 +1138,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
+      <c r="A16" s="9"/>
       <c r="B16" t="s">
         <v>30</v>
       </c>
@@ -1127,7 +1147,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
+      <c r="A17" s="9"/>
       <c r="B17" t="s">
         <v>31</v>
       </c>
@@ -1136,10 +1156,10 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="11"/>
+      <c r="A18" s="9"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="11"/>
+      <c r="A19" s="9"/>
       <c r="B19" t="s">
         <v>99</v>
       </c>
@@ -1148,7 +1168,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
+      <c r="A20" s="9"/>
       <c r="B20" t="s">
         <v>100</v>
       </c>
@@ -1157,7 +1177,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="11"/>
+      <c r="A21" s="9"/>
       <c r="B21" t="s">
         <v>101</v>
       </c>
@@ -1166,7 +1186,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="11"/>
+      <c r="A22" s="9"/>
       <c r="B22" t="s">
         <v>102</v>
       </c>
@@ -1175,7 +1195,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="11"/>
+      <c r="A23" s="9"/>
       <c r="B23" t="s">
         <v>103</v>
       </c>
@@ -1184,7 +1204,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="11"/>
+      <c r="A24" s="9"/>
       <c r="B24" t="s">
         <v>104</v>
       </c>
@@ -1193,7 +1213,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="11"/>
+      <c r="A25" s="9"/>
       <c r="B25" t="s">
         <v>105</v>
       </c>
@@ -1202,7 +1222,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="11"/>
+      <c r="A26" s="9"/>
       <c r="B26" t="s">
         <v>106</v>
       </c>
@@ -1211,7 +1231,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="11"/>
+      <c r="A27" s="9"/>
       <c r="B27" t="s">
         <v>107</v>
       </c>
@@ -1220,7 +1240,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="11"/>
+      <c r="A28" s="9"/>
       <c r="B28" t="s">
         <v>108</v>
       </c>
@@ -1229,10 +1249,10 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="11"/>
+      <c r="A29" s="9"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="11"/>
+      <c r="A30" s="9"/>
       <c r="B30" t="s">
         <v>109</v>
       </c>
@@ -1241,7 +1261,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="11"/>
+      <c r="A31" s="9"/>
       <c r="B31" t="s">
         <v>110</v>
       </c>
@@ -1250,7 +1270,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="11"/>
+      <c r="A32" s="9"/>
       <c r="B32" t="s">
         <v>111</v>
       </c>
@@ -1259,7 +1279,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="11"/>
+      <c r="A33" s="9"/>
       <c r="B33" t="s">
         <v>112</v>
       </c>
@@ -1268,7 +1288,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="11"/>
+      <c r="A34" s="9"/>
       <c r="B34" t="s">
         <v>113</v>
       </c>
@@ -1277,7 +1297,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="11"/>
+      <c r="A35" s="9"/>
       <c r="B35" t="s">
         <v>114</v>
       </c>
@@ -1286,7 +1306,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="11"/>
+      <c r="A36" s="9"/>
       <c r="B36" t="s">
         <v>115</v>
       </c>
@@ -1295,7 +1315,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="11"/>
+      <c r="A37" s="9"/>
       <c r="B37" t="s">
         <v>116</v>
       </c>
@@ -1304,7 +1324,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="11"/>
+      <c r="A38" s="9"/>
       <c r="B38" t="s">
         <v>117</v>
       </c>
@@ -1313,10 +1333,10 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="11"/>
+      <c r="A39" s="9"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="11"/>
+      <c r="A40" s="9"/>
       <c r="B40" t="s">
         <v>152</v>
       </c>
@@ -1325,7 +1345,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="11"/>
+      <c r="A41" s="9"/>
       <c r="B41" t="s">
         <v>153</v>
       </c>
@@ -1334,7 +1354,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="11"/>
+      <c r="A42" s="9"/>
       <c r="B42" t="s">
         <v>154</v>
       </c>
@@ -1343,7 +1363,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="11"/>
+      <c r="A43" s="9"/>
       <c r="B43" t="s">
         <v>155</v>
       </c>
@@ -1352,778 +1372,770 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="11"/>
+      <c r="A44" s="9"/>
       <c r="B44" t="s">
         <v>156</v>
       </c>
       <c r="C44" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="9"/>
+      <c r="B45" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="11"/>
-      <c r="B45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="9"/>
+      <c r="B46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="11"/>
-      <c r="B46" t="s">
-        <v>158</v>
-      </c>
-      <c r="C46" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="11"/>
+      <c r="A47" s="9"/>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="11"/>
+      <c r="A48" s="9"/>
       <c r="B48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="9"/>
+      <c r="B49" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="9"/>
+      <c r="B50" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="11"/>
-      <c r="B49" t="s">
-        <v>161</v>
-      </c>
-      <c r="C49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="11"/>
-    </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="11"/>
+      <c r="A51" s="9"/>
       <c r="B51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="9"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="9"/>
+      <c r="B53" t="s">
         <v>32</v>
       </c>
-      <c r="C51" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="11"/>
-      <c r="B52" t="s">
+      <c r="C53" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="9"/>
+      <c r="B54" t="s">
         <v>33</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C54" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="11"/>
-      <c r="B53" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="9"/>
+      <c r="B55" t="s">
         <v>34</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C55" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="11"/>
-      <c r="B54" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="9"/>
+      <c r="B56" t="s">
         <v>35</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C56" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="11"/>
-      <c r="B55" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="9"/>
+      <c r="B57" t="s">
         <v>36</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C57" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="11"/>
-      <c r="B56" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="9"/>
+      <c r="B58" t="s">
         <v>37</v>
       </c>
-      <c r="C56" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="11"/>
-      <c r="B57" t="s">
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="9"/>
+      <c r="B59" t="s">
         <v>38</v>
       </c>
-      <c r="C57" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="11"/>
-      <c r="B58" t="s">
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="9"/>
+      <c r="B60" t="s">
         <v>39</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C60" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="11"/>
-      <c r="B59" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="9"/>
+      <c r="B61" t="s">
         <v>40</v>
       </c>
-      <c r="C59" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="11"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="11"/>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="9"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="9"/>
+      <c r="B63" t="s">
         <v>118</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C63" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="11"/>
-      <c r="B62" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="9"/>
+      <c r="B64" t="s">
         <v>119</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C64" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="11"/>
-      <c r="B63" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="9"/>
+      <c r="B65" t="s">
         <v>120</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C65" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="11"/>
-      <c r="B64" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="9"/>
+      <c r="B66" t="s">
         <v>121</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C66" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="11"/>
-      <c r="B65" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="9"/>
+      <c r="B67" t="s">
         <v>122</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C67" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="11"/>
-      <c r="B66" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="9"/>
+      <c r="B68" t="s">
         <v>123</v>
       </c>
-      <c r="C66" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="11"/>
-      <c r="B67" t="s">
+      <c r="C68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="9"/>
+      <c r="B69" t="s">
         <v>124</v>
       </c>
-      <c r="C67" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="11"/>
-      <c r="B68" t="s">
+      <c r="C69" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="9"/>
+      <c r="B70" t="s">
         <v>125</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C70" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="11"/>
-      <c r="B69" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="9"/>
+      <c r="B71" t="s">
         <v>126</v>
       </c>
-      <c r="C69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="11"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="11"/>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="9"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="9"/>
+      <c r="B73" t="s">
         <v>41</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C73" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="11"/>
-      <c r="B72" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="9"/>
+      <c r="B74" t="s">
         <v>42</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C74" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="11"/>
-      <c r="B73" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="9"/>
+      <c r="B75" t="s">
         <v>43</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C75" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="11"/>
-      <c r="B74" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="9"/>
+      <c r="B76" t="s">
         <v>44</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C76" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="11"/>
-      <c r="B75" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="9"/>
+      <c r="B77" t="s">
         <v>45</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C77" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="11"/>
-      <c r="B76" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="9"/>
+      <c r="B78" t="s">
         <v>46</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C78" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="11"/>
-      <c r="B77" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="9"/>
+      <c r="B79" t="s">
         <v>47</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C79" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="11"/>
-      <c r="B78" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="9"/>
+      <c r="B80" t="s">
         <v>48</v>
       </c>
-      <c r="C78" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="11"/>
-      <c r="B79" t="s">
+      <c r="C80" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="9"/>
+      <c r="B81" t="s">
         <v>49</v>
       </c>
-      <c r="C79" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="11"/>
-      <c r="B80" t="s">
+      <c r="C81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="9"/>
+      <c r="B82" t="s">
         <v>50</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C82" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="11"/>
-      <c r="B81" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="9"/>
+      <c r="B83" t="s">
         <v>51</v>
       </c>
-      <c r="C81" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="11"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="11"/>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="9"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="9"/>
+      <c r="B85" t="s">
         <v>52</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C85" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="11"/>
-      <c r="B84" t="s">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="9"/>
+      <c r="B86" t="s">
         <v>53</v>
       </c>
-      <c r="C84" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="11"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="11"/>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="9"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="9"/>
+      <c r="B88" t="s">
+        <v>166</v>
+      </c>
+      <c r="C88" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="9"/>
+      <c r="B89" t="s">
+        <v>168</v>
+      </c>
+      <c r="C89" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="9"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="9"/>
+      <c r="B91" t="s">
+        <v>169</v>
+      </c>
+      <c r="C91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="9"/>
+      <c r="B92" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="9"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="9"/>
+      <c r="B94" t="s">
         <v>54</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C94" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" s="11"/>
-      <c r="B87" t="s">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="9"/>
+      <c r="B95" t="s">
         <v>55</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C95" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="11"/>
-      <c r="B88" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="9"/>
+      <c r="B96" t="s">
         <v>56</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C96" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" s="11"/>
-      <c r="B89" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="9"/>
+      <c r="B97" t="s">
         <v>57</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C97" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="11"/>
-      <c r="B90" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="9"/>
+      <c r="B98" t="s">
         <v>58</v>
       </c>
-      <c r="C90" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="11"/>
-      <c r="B91" t="s">
+      <c r="C98" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="9"/>
+      <c r="B99" t="s">
         <v>59</v>
       </c>
-      <c r="C91" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="11"/>
-      <c r="B92" t="s">
+      <c r="C99" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="9"/>
+      <c r="B100" t="s">
         <v>60</v>
       </c>
-      <c r="C92" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="11"/>
-      <c r="B93" t="s">
+      <c r="C100" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="9"/>
+      <c r="B101" t="s">
         <v>61</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C101" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" s="11"/>
-      <c r="B94" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="9"/>
+      <c r="B102" t="s">
         <v>62</v>
       </c>
-      <c r="C94" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="11"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" s="11"/>
-      <c r="B96" t="s">
+      <c r="C102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="9"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="9"/>
+      <c r="B104" t="s">
         <v>63</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C104" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="11"/>
-      <c r="B97" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="9"/>
+      <c r="B105" t="s">
         <v>64</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C105" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="11"/>
-      <c r="B98" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="9"/>
+      <c r="B106" t="s">
         <v>65</v>
-      </c>
-      <c r="C98" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="11"/>
-      <c r="B99" t="s">
-        <v>66</v>
-      </c>
-      <c r="C99" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="11"/>
-      <c r="B100" t="s">
-        <v>67</v>
-      </c>
-      <c r="C100" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="11"/>
-      <c r="B101" t="s">
-        <v>68</v>
-      </c>
-      <c r="C101" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="11"/>
-      <c r="B102" t="s">
-        <v>69</v>
-      </c>
-      <c r="C102" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="11"/>
-      <c r="B103" t="s">
-        <v>70</v>
-      </c>
-      <c r="C103" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" s="11"/>
-      <c r="B104" t="s">
-        <v>71</v>
-      </c>
-      <c r="C104" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="11"/>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="11"/>
-      <c r="B106" t="s">
-        <v>72</v>
       </c>
       <c r="C106" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" s="11"/>
+      <c r="A107" s="9"/>
       <c r="B107" t="s">
+        <v>66</v>
+      </c>
+      <c r="C107" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="9"/>
+      <c r="B108" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="9"/>
+      <c r="B109" t="s">
+        <v>68</v>
+      </c>
+      <c r="C109" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="9"/>
+      <c r="B110" t="s">
+        <v>69</v>
+      </c>
+      <c r="C110" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="9"/>
+      <c r="B111" t="s">
+        <v>70</v>
+      </c>
+      <c r="C111" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="9"/>
+      <c r="B112" t="s">
+        <v>71</v>
+      </c>
+      <c r="C112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="9"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="9"/>
+      <c r="B114" t="s">
+        <v>72</v>
+      </c>
+      <c r="C114" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="9"/>
+      <c r="B115" t="s">
         <v>73</v>
       </c>
-      <c r="C107" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" s="11"/>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" s="11"/>
-      <c r="B109" t="s">
+      <c r="C115" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="9"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="9"/>
+      <c r="B117" t="s">
         <v>127</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C117" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" s="11"/>
-      <c r="B110" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="9"/>
+      <c r="B118" t="s">
         <v>128</v>
       </c>
-      <c r="C110" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" s="11"/>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" s="11"/>
-      <c r="B112" t="s">
+      <c r="C118" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="9"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B120" t="s">
         <v>74</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C120" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" s="11"/>
-      <c r="B113" t="s">
-        <v>75</v>
-      </c>
-      <c r="C113" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" s="11"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="11"/>
-      <c r="B115" t="s">
-        <v>129</v>
-      </c>
-      <c r="C115" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" s="11"/>
-      <c r="B116" t="s">
-        <v>130</v>
-      </c>
-      <c r="C116" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="11"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" s="11"/>
-      <c r="B118" t="s">
-        <v>76</v>
-      </c>
-      <c r="C118" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="11"/>
-      <c r="B119" t="s">
-        <v>77</v>
-      </c>
-      <c r="C119" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C121" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B122" t="s">
-        <v>131</v>
-      </c>
-      <c r="C122" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B125" t="s">
-        <v>21</v>
-      </c>
-      <c r="C125" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C126" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B128" t="s">
-        <v>8</v>
-      </c>
-      <c r="C128" t="s">
-        <v>15</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B127" t="s">
+        <v>77</v>
+      </c>
+      <c r="C127" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="C129" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="C130" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="C131" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="C132" t="s">
-        <v>148</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="C133" t="s">
-        <v>148</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="C134" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B135" t="s">
-        <v>12</v>
-      </c>
-      <c r="C135" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C137" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
-        <v>162</v>
+        <v>10</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B140" t="s">
+        <v>132</v>
+      </c>
+      <c r="C140" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C141" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C142" t="s">
         <v>148</v>
@@ -2131,15 +2143,15 @@
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="C143" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
         <v>18</v>
@@ -2147,60 +2159,83 @@
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
       <c r="C145" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B146" t="s">
+        <v>135</v>
+      </c>
+      <c r="C146" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C147" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B148" t="s">
-        <v>85</v>
-      </c>
-      <c r="C148" t="s">
-        <v>149</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
-        <v>135</v>
+        <v>82</v>
+      </c>
+      <c r="C149" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
+      <c r="B150" t="s">
+        <v>137</v>
+      </c>
+      <c r="C150" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B151" s="8"/>
-      <c r="C151" s="8"/>
+      <c r="B151" t="s">
+        <v>83</v>
+      </c>
+      <c r="C151" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B152" s="8"/>
-      <c r="C152" s="8"/>
+      <c r="B152" t="s">
+        <v>138</v>
+      </c>
+      <c r="C152" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B153" s="8"/>
-      <c r="C153" s="8"/>
-    </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B154" s="8"/>
-      <c r="C154" s="8"/>
+      <c r="B153" t="s">
+        <v>139</v>
+      </c>
+      <c r="C153" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B155" s="9"/>
-      <c r="C155" s="9"/>
+      <c r="B155" t="s">
+        <v>84</v>
+      </c>
+      <c r="C155" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="156" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
+      <c r="B156" t="s">
+        <v>85</v>
+      </c>
+      <c r="C156" t="s">
+        <v>149</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
